--- a/docs/alpr_observation_counts.xlsx
+++ b/docs/alpr_observation_counts.xlsx
@@ -1046,7 +1046,7 @@
         <v>106</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H8" s="8">
         <f>IF(AND(ISNUMBER(F8),ISNUMBER(G8),G8&gt;0),F8/G8,"")</f>
